--- a/QCM3_3_PHY.xlsx
+++ b/QCM3_3_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5624B652-B359-4D53-A5D4-68A1AE351663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24D0CE2-EEAB-41FE-A42A-F2F010FEFD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,33 +63,15 @@
     <t>OptionE</t>
   </si>
   <si>
-    <t>À déterminer</t>
-  </si>
-  <si>
-    <t>$I_{max} = 150\text{ mA}$</t>
-  </si>
-  <si>
-    <t>$I_{max} = 120\text{ mA}$</t>
-  </si>
-  <si>
     <t>$I_{max} = 80\text{ mA}$</t>
   </si>
   <si>
     <t>$I_{max} = 100\text{ mA}$</t>
   </si>
   <si>
-    <t>$i(t) = A.e^{-t/\tau} + B$</t>
-  </si>
-  <si>
     <t>$i(t) = e^{-t/\tau}(A+B)$</t>
   </si>
   <si>
-    <t>$i(t) = A.e^{t/\tau} - B$</t>
-  </si>
-  <si>
-    <t>$i(t) = A + B.e^{-t/\tau}$</t>
-  </si>
-  <si>
     <t>$r = 100\ \Omega$</t>
   </si>
   <si>
@@ -114,24 +96,9 @@
     <t>$\tau = \frac{R+r}{L}$</t>
   </si>
   <si>
-    <t>$L = -R \cdot u_{AM} \cdot dt$</t>
-  </si>
-  <si>
-    <t>$L = -R \cdot \frac{u_{BM}}{dt}$</t>
-  </si>
-  <si>
-    <t>$L = -R \frac{du_{BM}}{dt} u_{AM}$</t>
-  </si>
-  <si>
-    <t>$L = -R \cdot \frac{u_{AM}}{\frac{du_{BM}}{dt}}$</t>
-  </si>
-  <si>
     <t>$L = 50\text{ mH}$</t>
   </si>
   <si>
-    <t>$L = 30\text{ mH}$</t>
-  </si>
-  <si>
     <t>$L = 20\text{ mH}$</t>
   </si>
   <si>
@@ -150,18 +117,9 @@
     <t>$I_{max} = 10\text{ mA}$</t>
   </si>
   <si>
-    <t>$E_{mag} = 2,5 \cdot 10^{-6}\text{ J}$</t>
-  </si>
-  <si>
     <t>$E_{mag} = 1,52 \cdot 10^{-6}\text{ J}$</t>
   </si>
   <si>
-    <t>$E_{mag} = 3 \cdot 10^{-6}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$E_{mag} = 1,5 \cdot 10^{-6}\text{ J}$</t>
-  </si>
-  <si>
     <t>$\frac{di}{dt} + \frac{R+r}{L}i = \frac{E}{R+r}$</t>
   </si>
   <si>
@@ -174,33 +132,15 @@
     <t>$\frac{di}{dt} + \frac{R+r}{L}i = 0$</t>
   </si>
   <si>
-    <t>$i(t) = \frac{E}{r} e^{-t/\tau}$</t>
-  </si>
-  <si>
-    <t>$i(t) = \frac{E}{R+r}(1 - e^{t/\tau})$</t>
-  </si>
-  <si>
     <t>$i(t) = \frac{R \cdot E}{R+r}(1 - e^{-t/\tau})$</t>
   </si>
   <si>
     <t>$i(t) = \frac{E}{R+r}(1 - e^{-t/\tau})$</t>
   </si>
   <si>
-    <t>$U_L = \frac{r}{R}E$</t>
-  </si>
-  <si>
     <t>$U_L = \frac{r}{R+r}E$</t>
   </si>
   <si>
-    <t>$U_L = (R+r)E$</t>
-  </si>
-  <si>
-    <t>$U_L = \frac{R}{R+r}E$</t>
-  </si>
-  <si>
-    <t>$L = 0,2\text{ H}$</t>
-  </si>
-  <si>
     <t>$L = 0,3\text{ H}$</t>
   </si>
   <si>
@@ -258,9 +198,6 @@
     <t>$\tau = \frac{L}{R+r+r'}$</t>
   </si>
   <si>
-    <t>$\tau = \frac{1}{r+r'}$</t>
-  </si>
-  <si>
     <t>$U_{BC} = L\frac{di}{dt} + r \cdot i$</t>
   </si>
   <si>
@@ -295,10 +232,6 @@
   </si>
   <si>
     <t>$I_P = 70\text{ mA}$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Dipôle RL : &lt;/b&gt;&lt;/center&gt;
-On considère l'association en série d'une bobine d'inductance $L = 400\text{ mH}$ et de résistance $r$, avec un conducteur ohmique de résistance $R = 100\ \Omega$. La tension $u$ aux bornes de l'association est telle que : pour $t &lt; 0, u = 0$ ; pour $t &gt; 0, u = E = 15\text{ V}$. On obtient l'enregistrement de l'intensité $i$ traversant le circuit, en fonction du temps.</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Un générateur GBF : &lt;/b&gt;&lt;/center&gt;
@@ -309,94 +242,166 @@
 Une bobine de résistance $r = 10\ \Omega$ et d'inductance $L$ est montée en série avec une résistance $R = 40\ \Omega$ et un générateur de tension continue de f.e.m $E = 6,0\text{ V}$. On a branché un oscilloscope aux bornes de la bobine. La courbe ci-contre représente la tension aux bornes de la bobine lorsqu'on a fermé l'interrupteur K.</t>
   </si>
   <si>
+    <t>L'intensité en régime permanent est :</t>
+  </si>
+  <si>
+    <t>L'intensité $i$ dans le circuit peut s'exprimer sous la forme (avec $A$ et $B$ constantes) :</t>
+  </si>
+  <si>
+    <t>La résistance de la bobine est :</t>
+  </si>
+  <si>
+    <t>La constante de temps du circuit est :</t>
+  </si>
+  <si>
+    <t>L'expression de $L$ est :</t>
+  </si>
+  <si>
+    <t>L'inductance $L$ de la bobine a pour valeur :</t>
+  </si>
+  <si>
+    <t>L'intensité maximale a pour valeur :</t>
+  </si>
+  <si>
+    <t>L'énergie emmagasinée par la bobine a pour valeur :</t>
+  </si>
+  <si>
+    <t>L'équation différentielle à laquelle obéit $i(t)$, l'intensité du courant à la fermeture du circuit :</t>
+  </si>
+  <si>
+    <t>La solution de cette équation différentielle est :</t>
+  </si>
+  <si>
+    <t>L'expression de $U_L$ en régime permanent :</t>
+  </si>
+  <si>
+    <t>La valeur de $L$ est :</t>
+  </si>
+  <si>
+    <t>La tension aux bornes du conducteur ohmique a pour expression :</t>
+  </si>
+  <si>
+    <t>La tension aux bornes de la bobine a pour expression :</t>
+  </si>
+  <si>
+    <t>La fréquence du signal vaut :</t>
+  </si>
+  <si>
+    <t>La constante de temps $\tau$ du circuit est :</t>
+  </si>
+  <si>
+    <t>L'expression de la tension aux bornes de la bobine est :</t>
+  </si>
+  <si>
+    <t>En régime permanent :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Dipôle RL : &lt;/b&gt;&lt;/center&gt;
+On considère l'association en série d'une bobine d'inductance $L = 400\text{ mH}$ et de résistance $r$, avec un conducteur ohmique de résistance $R = 100\ \Omega$. La tension $u$ aux bornes de l'association est telle que : 
+&lt;br&gt; * pour $t &lt; 0, u = 0$ ; 
+&lt;br&gt; * pour $t &gt; 0, u = E = 15\text{ V}$. 
+&lt;br&gt;On obtient l'enregistrement de l'intensité $i$ traversant le circuit, en fonction du temps.</t>
+  </si>
+  <si>
+    <t>$I_{max} = 0\text{ mA}$</t>
+  </si>
+  <si>
+    <t>$i(t) = A.e^{t/\tau} + B$</t>
+  </si>
+  <si>
+    <t>$i(t) = Ae^{-t/\tau} - B$</t>
+  </si>
+  <si>
+    <t>$i(t) = A + B.e^{t/\tau}$</t>
+  </si>
+  <si>
+    <t>$\tau = \frac{R}{L}$</t>
+  </si>
+  <si>
+    <t>$L = \frac{-R \cdot du_{AM}}{u_{BM} \cdot dt}$</t>
+  </si>
+  <si>
+    <t>$L = \frac{-R \cdot du_{BM}}{u_{AM} \cdot dt}$</t>
+  </si>
+  <si>
+    <t>$L = \frac{-R \cdot u_{BM}}{du_{AM}} \cdot dt$</t>
+  </si>
+  <si>
+    <t>$L = \frac{-R \cdot u_{AM}}{du_{BM}} \cdot dt$</t>
+  </si>
+  <si>
+    <t>$L = 100\text{ mH}$</t>
+  </si>
+  <si>
+    <t>$E_{mag} = 3,1 \cdot 10^{-6}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$E_{mag} = 3,1 \cdot 10^{-4}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$E_{mag} = 1,52 \cdot 10^{-4}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$i(t) = \frac{E}{R + r} e^{-t/\tau}$</t>
+  </si>
+  <si>
+    <t>$i(t) = \frac{rE}{R+r}(1 - e^{-t/\tau})$</t>
+  </si>
+  <si>
+    <t>$U_L = \frac{R}{R + r}E$</t>
+  </si>
+  <si>
+    <t>$U_L = \frac{R + r}{r}E$</t>
+  </si>
+  <si>
+    <t>$U_L = \frac{R + r}{R}E$</t>
+  </si>
+  <si>
+    <t>$L = 0,25\text{ H}$</t>
+  </si>
+  <si>
+    <t>$L = 0,4\text{ H}$</t>
+  </si>
+  <si>
     <t>&lt;center&gt;&lt;b&gt;Signaux triangulaires : &lt;/b&gt;&lt;/center&gt;
-On réalise le circuit ci-dessous (Figure 1), comprenant un générateur G de signaux triangulaires isolé de la masse, une résistance R et une bobine d'inductance L et de résistance négligeable par rapport à la résistance R. À l'aide d'une interface et d'un ordinateur, on visualise les variations de la tension $u_{BM}$ en fonction du temps (Figure 2). Donnée : $R = 100\ \Omega$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Un générateur de tension de f.é.m. E et de résistance r : &lt;/b&gt;&lt;/center&gt;
+On réalise le circuit ci-dessous (Figure 1), comprenant un générateur G de signaux triangulaires isolé de la masse, une résistance R et une bobine d'inductance L et de résistance négligeable par rapport à la résistance R. À l'aide d'une interface et d'un ordinateur, on visualise les variations de la tension $u_{BM}$ en fonction du temps (Figure 2). 
+&lt;br&gt;Donnée : $R = 100\ \Omega$.</t>
+  </si>
+  <si>
+    <t>Pour $0 &lt; t &lt; 10\text{ ms}$, la tension $u_{AM}$ relevée a pour valeur $-0,10\text{ V}$. 
+&lt;br&gt;L'inductance de la bobine a pour valeur :</t>
+  </si>
+  <si>
+    <t>$\tau = \frac{L}{r+r'}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un générateur de tension de f.é.m. E et de résistance r : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 On réalise le circuit suivant comprenant un générateur de tension de f.é.m. E et de résistance r, une bobine inductive d'inductance L et de résistance r' et un conducteur ohmique de résistance R. On place un interrupteur K. A $t = 0$ alors que la bobine n'a pas emmagasiné d'énergie on ferme l'interrupteur K. $E = 9,0\text{ V} ; R = 87\ \Omega ; r = 1,0\ \Omega ; r' = 12\ \Omega$.</t>
   </si>
   <si>
-    <t>L'intensité en régime permanent est :</t>
-  </si>
-  <si>
-    <t>L'intensité $i$ dans le circuit peut s'exprimer sous la forme (avec $A$ et $B$ constantes) :</t>
-  </si>
-  <si>
-    <t>La résistance de la bobine est :</t>
-  </si>
-  <si>
-    <t>La constante de temps du circuit est :</t>
-  </si>
-  <si>
-    <t>L'expression de $L$ est :</t>
-  </si>
-  <si>
-    <t>L'inductance $L$ de la bobine a pour valeur :</t>
-  </si>
-  <si>
-    <t>L'intensité maximale a pour valeur :</t>
-  </si>
-  <si>
-    <t>L'énergie emmagasinée par la bobine a pour valeur :</t>
-  </si>
-  <si>
-    <t>L'équation différentielle à laquelle obéit $i(t)$, l'intensité du courant à la fermeture du circuit :</t>
-  </si>
-  <si>
-    <t>La solution de cette équation différentielle est :</t>
-  </si>
-  <si>
-    <t>L'expression de $U_L$ en régime permanent :</t>
-  </si>
-  <si>
-    <t>La valeur de $L$ est :</t>
-  </si>
-  <si>
-    <t>La tension aux bornes du conducteur ohmique a pour expression :</t>
-  </si>
-  <si>
-    <t>La tension aux bornes de la bobine a pour expression :</t>
-  </si>
-  <si>
-    <t>Pour $0 &lt; t &lt; 10\text{ ms}$, la tension $u_{AM}$ relevée a pour valeur $-0,10\text{ V}$. L'inductance de la bobine a pour valeur :</t>
-  </si>
-  <si>
-    <t>La fréquence du signal vaut :</t>
-  </si>
-  <si>
-    <t>La constante de temps $\tau$ du circuit est :</t>
-  </si>
-  <si>
-    <t>L'expression de la tension aux bornes de la bobine est :</t>
-  </si>
-  <si>
-    <t>A $t = 0$, la tension $U_{BC}$ vaut :</t>
-  </si>
-  <si>
-    <t>En régime permanent :</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_3_Q1</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_3_Q2</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_3_Q3</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_3_Q4</t>
-  </si>
-  <si>
-    <t>PHY_QCM3_3_Q5</t>
+    <t>A $t = 0^+$, la tension $U_{BC}$ vaut :</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_3_Q1.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_3_Q2.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_3_Q3.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_3_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM3_3_Q5.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,12 +422,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -468,7 +467,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -530,11 +529,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -552,25 +562,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -921,31 +928,31 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="H2" s="8"/>
-      <c r="I2" s="10" t="s">
-        <v>12</v>
+      <c r="I2" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>115</v>
@@ -953,111 +960,111 @@
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
+      <c r="A3" s="10"/>
       <c r="B3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H4" s="6"/>
-      <c r="I4" s="13" t="s">
-        <v>12</v>
+      <c r="I4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>116</v>
@@ -1065,111 +1072,111 @@
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="13" t="s">
-        <v>12</v>
+      <c r="I7" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="13" t="s">
-        <v>12</v>
+      <c r="I8" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="G9" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="13" t="s">
-        <v>12</v>
+      <c r="I9" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>117</v>
@@ -1177,288 +1184,288 @@
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="13" t="s">
-        <v>12</v>
+      <c r="I13" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>63</v>
+        <v>43</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
-        <v>64</v>
+      <c r="I14" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="J14" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H16" s="6"/>
-      <c r="I16" s="13" t="s">
-        <v>12</v>
+      <c r="I16" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H17" s="6"/>
-      <c r="I17" s="13" t="s">
-        <v>12</v>
+      <c r="I17" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="J18" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
